--- a/salidas/empresas/GE.xlsx
+++ b/salidas/empresas/GE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>96.39455413818359</v>
+        <v>96.39454650878906</v>
       </c>
       <c r="C2" t="n">
         <v>156.9523315429688</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>97.47214508056641</v>
+        <v>97.47212219238281</v>
       </c>
       <c r="C3" t="n">
         <v>157.5274200439453</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>103.1360092163086</v>
+        <v>103.1360015869141</v>
       </c>
       <c r="C4" t="n">
         <v>166.6809692382812</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>102.5725479125977</v>
+        <v>102.5726013183594</v>
       </c>
       <c r="C5" t="n">
         <v>165.7704162597656</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>101.5940017700195</v>
+        <v>101.5939865112305</v>
       </c>
       <c r="C6" t="n">
         <v>164.1889038085938</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>98.47016143798828</v>
+        <v>98.47017669677734</v>
       </c>
       <c r="C7" t="n">
         <v>157.958740234375</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>97.66357421875</v>
+        <v>97.66356658935547</v>
       </c>
       <c r="C8" t="n">
         <v>156.6647796630859</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>101.7564468383789</v>
+        <v>101.7564849853516</v>
       </c>
       <c r="C9" t="n">
         <v>163.2304229736328</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>106.2193222045898</v>
+        <v>106.2193374633789</v>
       </c>
       <c r="C10" t="n">
         <v>169.1730346679688</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>105.6476516723633</v>
+        <v>105.6475677490234</v>
       </c>
       <c r="C11" t="n">
         <v>168.2624816894531</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>106.1592102050781</v>
+        <v>106.1591796875</v>
       </c>
       <c r="C12" t="n">
         <v>169.0771942138672</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>112.7945098876953</v>
+        <v>112.7944717407227</v>
       </c>
       <c r="C13" t="n">
         <v>178.3265991210938</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>109.2781600952148</v>
+        <v>109.2781066894531</v>
       </c>
       <c r="C14" t="n">
         <v>172.7673645019531</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>106.6540679931641</v>
+        <v>106.6540832519531</v>
       </c>
       <c r="C15" t="n">
         <v>167.3039855957031</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>112.6115341186523</v>
+        <v>112.6115798950195</v>
       </c>
       <c r="C17" t="n">
         <v>176.6492462158203</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>114.8112030029297</v>
+        <v>114.8112411499023</v>
       </c>
       <c r="C18" t="n">
         <v>180.0997924804688</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>117.7940368652344</v>
+        <v>117.7940521240234</v>
       </c>
       <c r="C19" t="n">
         <v>183.4544982910156</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>119.2710266113281</v>
+        <v>119.2709655761719</v>
       </c>
       <c r="C20" t="n">
         <v>185.7548675537109</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>119.6095504760742</v>
+        <v>119.6095657348633</v>
       </c>
       <c r="C21" t="n">
         <v>186.2820434570312</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>128.2544708251953</v>
+        <v>128.2545471191406</v>
       </c>
       <c r="C22" t="n">
         <v>198.4069061279297</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>127.5110092163086</v>
+        <v>127.5109710693359</v>
       </c>
       <c r="C23" t="n">
         <v>197.2567291259766</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>115.8223037719727</v>
+        <v>115.8222732543945</v>
       </c>
       <c r="C25" t="n">
         <v>177.6556549072266</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>110.4795303344727</v>
+        <v>110.4795227050781</v>
       </c>
       <c r="C26" t="n">
         <v>169.4605865478516</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>104.4860000610352</v>
+        <v>104.4859466552734</v>
       </c>
       <c r="C27" t="n">
         <v>158.8213806152344</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>116.687629699707</v>
+        <v>116.6876068115234</v>
       </c>
       <c r="C28" t="n">
         <v>177.3681030273438</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>103.098747253418</v>
+        <v>103.0987396240234</v>
       </c>
       <c r="C29" t="n">
         <v>156.7127075195312</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>96.85606384277344</v>
+        <v>96.8560791015625</v>
       </c>
       <c r="C30" t="n">
         <v>147.2236785888672</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>85.08500671386719</v>
+        <v>85.08499145507812</v>
       </c>
       <c r="C31" t="n">
         <v>127.91015625</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>90.18563842773438</v>
+        <v>90.18564605712891</v>
       </c>
       <c r="C32" t="n">
         <v>135.5780487060547</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>82.38323974609375</v>
+        <v>82.38328552246094</v>
       </c>
       <c r="C34" t="n">
         <v>122.2071533203125</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>55.47139358520508</v>
+        <v>55.47138214111328</v>
       </c>
       <c r="C36" t="n">
         <v>82.28614807128906</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>53.34410095214844</v>
+        <v>53.34410858154297</v>
       </c>
       <c r="C37" t="n">
         <v>77.63748931884766</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>39.94221115112305</v>
+        <v>39.94222259521484</v>
       </c>
       <c r="C38" t="n">
         <v>58.13226318359375</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.84552001953125</v>
+        <v>28.84550476074219</v>
       </c>
       <c r="C39" t="n">
         <v>40.78364181518555</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>34.26889038085938</v>
+        <v>34.26888275146484</v>
       </c>
       <c r="C40" t="n">
         <v>48.45154190063477</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>42.87846374511719</v>
+        <v>42.87846755981445</v>
       </c>
       <c r="C41" t="n">
         <v>60.62433242797852</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>45.69183731079102</v>
+        <v>45.69183349609375</v>
       </c>
       <c r="C42" t="n">
         <v>64.60205841064453</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>40.05311584472656</v>
+        <v>40.05310821533203</v>
       </c>
       <c r="C43" t="n">
         <v>56.16736602783203</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>45.79449462890625</v>
+        <v>45.79450988769531</v>
       </c>
       <c r="C44" t="n">
         <v>64.21865844726562</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>47.50326156616211</v>
+        <v>47.50326919555664</v>
       </c>
       <c r="C45" t="n">
         <v>66.61488342285156</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>56.4473991394043</v>
+        <v>56.44740676879883</v>
       </c>
       <c r="C46" t="n">
         <v>78.69181823730469</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>49.02189254760742</v>
+        <v>49.02191925048828</v>
       </c>
       <c r="C47" t="n">
         <v>68.34015655517578</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>55.07231140136719</v>
+        <v>55.07230377197266</v>
       </c>
       <c r="C48" t="n">
         <v>76.77484893798828</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>52.35089874267578</v>
+        <v>52.35091018676758</v>
       </c>
       <c r="C49" t="n">
         <v>72.50957489013672</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>55.63797378540039</v>
+        <v>55.63798904418945</v>
       </c>
       <c r="C50" t="n">
         <v>77.06239318847656</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>55.91565704345703</v>
+        <v>55.91567611694336</v>
       </c>
       <c r="C51" t="n">
         <v>76.96654510498047</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>63.3664436340332</v>
+        <v>63.36645126342773</v>
       </c>
       <c r="C52" t="n">
         <v>87.22235870361328</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>65.66432189941406</v>
+        <v>65.66434478759766</v>
       </c>
       <c r="C53" t="n">
         <v>90.38536834716797</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>56.92535781860352</v>
+        <v>56.92534637451172</v>
       </c>
       <c r="C54" t="n">
         <v>78.35635375976562</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>50.52447128295898</v>
+        <v>50.52449417114258</v>
       </c>
       <c r="C55" t="n">
         <v>69.10694885253906</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>56.48089599609375</v>
+        <v>56.48093032836914</v>
       </c>
       <c r="C56" t="n">
         <v>77.25408935546875</v>
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>57.35761260986328</v>
+        <v>57.35759735107422</v>
       </c>
       <c r="C58" t="n">
         <v>77.87710571289062</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>56.5457878112793</v>
+        <v>56.54581451416016</v>
       </c>
       <c r="C59" t="n">
         <v>76.77484893798828</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>55.87516403198242</v>
+        <v>55.87514495849609</v>
       </c>
       <c r="C60" t="n">
         <v>75.86428070068359</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>65.067138671875</v>
+        <v>65.06710815429688</v>
       </c>
       <c r="C61" t="n">
         <v>87.65367889404297</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>71.64854431152344</v>
+        <v>71.64852142333984</v>
       </c>
       <c r="C62" t="n">
         <v>96.51969146728516</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>74.93846893310547</v>
+        <v>74.93843078613281</v>
       </c>
       <c r="C63" t="n">
         <v>100.2577896118164</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>71.82199096679688</v>
+        <v>71.82197570800781</v>
       </c>
       <c r="C64" t="n">
         <v>96.08837127685547</v>
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>70.35332489013672</v>
+        <v>70.35330200195312</v>
       </c>
       <c r="C66" t="n">
         <v>94.12346649169922</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>68.11483001708984</v>
+        <v>68.11482238769531</v>
       </c>
       <c r="C67" t="n">
         <v>90.38536834716797</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>64.68378448486328</v>
+        <v>64.68381500244141</v>
       </c>
       <c r="C68" t="n">
         <v>85.83255004882812</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>58.90525817871094</v>
+        <v>58.9052619934082</v>
       </c>
       <c r="C69" t="n">
         <v>78.16465759277344</v>
@@ -1952,7 +1964,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>60.92867660522461</v>
+        <v>60.92869567871094</v>
       </c>
       <c r="C71" t="n">
         <v>80.08162689208984</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>58.01169967651367</v>
+        <v>58.0117073059082</v>
       </c>
       <c r="C72" t="n">
         <v>76.2476806640625</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>65.93781280517578</v>
+        <v>65.93779754638672</v>
       </c>
       <c r="C73" t="n">
         <v>85.83255004882812</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>68.88314056396484</v>
+        <v>68.88311004638672</v>
       </c>
       <c r="C74" t="n">
         <v>89.66650390625</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>70.75522613525391</v>
+        <v>70.75517272949219</v>
       </c>
       <c r="C75" t="n">
         <v>91.29592895507812</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>74.543701171875</v>
+        <v>74.54365539550781</v>
       </c>
       <c r="C76" t="n">
         <v>96.18421936035156</v>
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>70.90380096435547</v>
+        <v>70.90376281738281</v>
       </c>
       <c r="C78" t="n">
         <v>91.48763275146484</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>78.28218078613281</v>
+        <v>78.28216552734375</v>
       </c>
       <c r="C79" t="n">
         <v>99.87439727783203</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>77.94413757324219</v>
+        <v>77.94414520263672</v>
       </c>
       <c r="C80" t="n">
         <v>99.44307708740234</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>77.79385375976562</v>
+        <v>77.79383850097656</v>
       </c>
       <c r="C81" t="n">
         <v>99.25138092041016</v>
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>79.71275329589844</v>
+        <v>79.71276092529297</v>
       </c>
       <c r="C83" t="n">
         <v>100.9287338256836</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>79.97765350341797</v>
+        <v>79.97763824462891</v>
       </c>
       <c r="C84" t="n">
         <v>101.2641983032227</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>80.17280578613281</v>
+        <v>80.17282867431641</v>
       </c>
       <c r="C85" t="n">
         <v>100.59326171875</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>85.10002899169922</v>
+        <v>85.10002136230469</v>
       </c>
       <c r="C86" t="n">
         <v>106.775505065918</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>89.41616821289062</v>
+        <v>89.41616058349609</v>
       </c>
       <c r="C87" t="n">
         <v>111.2803955078125</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>89.03108978271484</v>
+        <v>89.03107452392578</v>
       </c>
       <c r="C88" t="n">
         <v>110.801155090332</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>90.01383209228516</v>
+        <v>90.01386260986328</v>
       </c>
       <c r="C91" t="n">
         <v>111.1366195678711</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>94.5941162109375</v>
+        <v>94.59410095214844</v>
       </c>
       <c r="C92" t="n">
         <v>116.7917022705078</v>
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>93.44514465332031</v>
+        <v>93.44512176513672</v>
       </c>
       <c r="C94" t="n">
         <v>114.491325378418</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>102.2459487915039</v>
+        <v>102.2459716796875</v>
       </c>
       <c r="C95" t="n">
         <v>125.2743148803711</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>104.2798843383789</v>
+        <v>104.279899597168</v>
       </c>
       <c r="C96" t="n">
         <v>127.7663803100586</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>110.5257339477539</v>
+        <v>110.5257797241211</v>
       </c>
       <c r="C97" t="n">
         <v>134.3320159912109</v>
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>101.3088073730469</v>
+        <v>101.308837890625</v>
       </c>
       <c r="C99" t="n">
         <v>122.0633773803711</v>
@@ -2822,7 +2834,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>106.5592193603516</v>
+        <v>106.5592346191406</v>
       </c>
       <c r="C102" t="n">
         <v>128.389404296875</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>105.3929214477539</v>
+        <v>105.392936706543</v>
       </c>
       <c r="C103" t="n">
         <v>125.9452514648438</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>100.8612213134766</v>
+        <v>100.8611831665039</v>
       </c>
       <c r="C104" t="n">
         <v>120.5298004150391</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>104.1898193359375</v>
+        <v>104.1898345947266</v>
       </c>
       <c r="C105" t="n">
         <v>124.5075225830078</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>103.6138000488281</v>
+        <v>103.6137924194336</v>
       </c>
       <c r="C106" t="n">
         <v>122.7822494506836</v>
@@ -3025,7 +3037,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>103.1604614257812</v>
+        <v>103.1604766845703</v>
       </c>
       <c r="C109" t="n">
         <v>121.1048965454102</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>97.52684783935547</v>
+        <v>97.52686309814453</v>
       </c>
       <c r="C110" t="n">
         <v>114.491325378418</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>107.0750961303711</v>
+        <v>107.075080871582</v>
       </c>
       <c r="C111" t="n">
         <v>124.5554504394531</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>102.2136383056641</v>
+        <v>102.2136306762695</v>
       </c>
       <c r="C112" t="n">
         <v>118.9003677368164</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>111.5657119750977</v>
+        <v>111.5657272338867</v>
       </c>
       <c r="C113" t="n">
         <v>129.7792053222656</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>112.3484802246094</v>
+        <v>112.348518371582</v>
       </c>
       <c r="C114" t="n">
         <v>130.6897735595703</v>
@@ -3255,11 +3267,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>110.3956909179688</v>
+        <v>110.3956985473633</v>
       </c>
       <c r="C115" t="n">
         <v>127.3350601196289</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>108.4429016113281</v>
+        <v>108.4428863525391</v>
       </c>
       <c r="C116" t="n">
         <v>125.0826187133789</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>103.1246185302734</v>
+        <v>103.1245956420898</v>
       </c>
       <c r="C117" t="n">
         <v>118.9482955932617</v>
@@ -3336,11 +3348,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>105.7243576049805</v>
+        <v>105.7243728637695</v>
       </c>
       <c r="C118" t="n">
         <v>120.8652725219727</v>
@@ -3363,7 +3375,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>125.5109710693359</v>
+        <v>125.5109329223633</v>
       </c>
       <c r="C120" t="n">
         <v>143.4855804443359</v>
@@ -3417,11 +3429,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>131.5601348876953</v>
+        <v>131.5601654052734</v>
       </c>
       <c r="C121" t="n">
         <v>149.284423828125</v>
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>124.0562744140625</v>
+        <v>124.0562896728516</v>
       </c>
       <c r="C123" t="n">
         <v>139.6516265869141</v>
@@ -3498,11 +3510,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>135.3380126953125</v>
+        <v>135.3379669189453</v>
       </c>
       <c r="C124" t="n">
         <v>152.3515777587891</v>
@@ -3525,7 +3537,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3552,11 +3564,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>128.6967163085938</v>
+        <v>128.6966705322266</v>
       </c>
       <c r="C126" t="n">
         <v>144.8753814697266</v>
@@ -3581,11 +3593,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>135.0334930419922</v>
+        <v>135.0335388183594</v>
       </c>
       <c r="C127" t="n">
         <v>150.8659362792969</v>
@@ -3610,11 +3622,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>133.5750885009766</v>
+        <v>133.5751037597656</v>
       </c>
       <c r="C128" t="n">
         <v>149.2364959716797</v>
@@ -3639,11 +3651,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>134.0040893554688</v>
+        <v>134.0040435791016</v>
       </c>
       <c r="C129" t="n">
         <v>149.7157440185547</v>
@@ -3668,11 +3680,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>128.0466613769531</v>
+        <v>128.0466918945312</v>
       </c>
       <c r="C130" t="n">
         <v>141.9519958496094</v>
@@ -3697,11 +3709,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>125.7987213134766</v>
+        <v>125.7987442016602</v>
       </c>
       <c r="C131" t="n">
         <v>139.4599304199219</v>
@@ -3726,7 +3738,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3755,11 +3767,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>137.6342620849609</v>
+        <v>137.6342926025391</v>
       </c>
       <c r="C133" t="n">
         <v>151.4410247802734</v>
@@ -3784,11 +3796,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>129.3587951660156</v>
+        <v>129.3587799072266</v>
       </c>
       <c r="C134" t="n">
         <v>142.3353881835938</v>
@@ -3813,11 +3825,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>130.8734741210938</v>
+        <v>130.8734893798828</v>
       </c>
       <c r="C135" t="n">
         <v>142.8625640869141</v>
@@ -3842,11 +3854,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>130.82958984375</v>
+        <v>130.8295440673828</v>
       </c>
       <c r="C136" t="n">
         <v>142.8146362304688</v>
@@ -3871,11 +3883,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>127.2734680175781</v>
+        <v>127.2734909057617</v>
       </c>
       <c r="C137" t="n">
         <v>138.9327545166016</v>
@@ -3900,11 +3912,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>120.2051544189453</v>
+        <v>120.2051849365234</v>
       </c>
       <c r="C138" t="n">
         <v>131.2169342041016</v>
@@ -3929,11 +3941,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>119.5810852050781</v>
+        <v>119.5811157226562</v>
       </c>
       <c r="C139" t="n">
         <v>129.4437408447266</v>
@@ -3958,11 +3970,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>113.3829116821289</v>
+        <v>113.3828811645508</v>
       </c>
       <c r="C140" t="n">
         <v>122.7343215942383</v>
@@ -3987,11 +3999,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>108.6899642944336</v>
+        <v>108.6899871826172</v>
       </c>
       <c r="C141" t="n">
         <v>117.6543350219727</v>
@@ -4016,11 +4028,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>108.1214904785156</v>
+        <v>108.1214981079102</v>
       </c>
       <c r="C142" t="n">
         <v>115.8811340332031</v>
@@ -4045,7 +4057,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4074,11 +4086,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>81.78421783447266</v>
+        <v>81.78423309326172</v>
       </c>
       <c r="C144" t="n">
         <v>87.65367889404297</v>
@@ -4103,11 +4115,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.56687164306641</v>
+        <v>78.56686401367188</v>
       </c>
       <c r="C145" t="n">
         <v>83.62802886962891</v>
@@ -4132,11 +4144,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>72.80379486083984</v>
+        <v>72.80380249023438</v>
       </c>
       <c r="C146" t="n">
         <v>77.49371337890625</v>
@@ -4161,11 +4173,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>64.05461883544922</v>
+        <v>64.05462646484375</v>
       </c>
       <c r="C147" t="n">
         <v>67.62129211425781</v>
@@ -4188,11 +4200,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>61.19463348388672</v>
+        <v>61.19462966918945</v>
       </c>
       <c r="C148" t="n">
         <v>64.60205841064453</v>
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>63.87303924560547</v>
+        <v>63.87302398681641</v>
       </c>
       <c r="C149" t="n">
         <v>67.42959594726562</v>
@@ -4242,11 +4254,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>63.91840744018555</v>
+        <v>63.91843032836914</v>
       </c>
       <c r="C150" t="n">
         <v>67.47751617431641</v>
@@ -4269,11 +4281,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>62.33316802978516</v>
+        <v>62.33316040039062</v>
       </c>
       <c r="C151" t="n">
         <v>65.22507476806641</v>
@@ -4296,11 +4308,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>62.42476272583008</v>
+        <v>62.42475891113281</v>
       </c>
       <c r="C152" t="n">
         <v>65.3209228515625</v>
@@ -4323,11 +4335,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>59.26459503173828</v>
+        <v>59.26459121704102</v>
       </c>
       <c r="C153" t="n">
         <v>62.01414108276367</v>
@@ -4350,11 +4362,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>52.20051956176758</v>
+        <v>52.20053482055664</v>
       </c>
       <c r="C154" t="n">
         <v>54.10661697387695</v>
@@ -4377,7 +4389,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4404,11 +4416,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>34.67704772949219</v>
+        <v>34.67705535888672</v>
       </c>
       <c r="C156" t="n">
         <v>35.94327926635742</v>
@@ -4431,11 +4443,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>35.04884338378906</v>
+        <v>35.04884719848633</v>
       </c>
       <c r="C157" t="n">
         <v>36.27875137329102</v>
@@ -4458,7 +4470,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>50.02956008911133</v>
+        <v>50.02956390380859</v>
       </c>
       <c r="C159" t="n">
         <v>51.78516006469727</v>
@@ -4512,7 +4524,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>49.02210235595703</v>
+        <v>49.02210998535156</v>
       </c>
       <c r="C161" t="n">
         <v>50.68865203857422</v>
@@ -4566,11 +4578,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.50330352783203</v>
+        <v>45.50331115722656</v>
       </c>
       <c r="C162" t="n">
         <v>47.05023193359375</v>
@@ -4593,11 +4605,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>50.66151428222656</v>
+        <v>50.6614990234375</v>
       </c>
       <c r="C163" t="n">
         <v>52.33341598510742</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>50.42025375366211</v>
+        <v>50.42026519775391</v>
       </c>
       <c r="C164" t="n">
         <v>52.08420944213867</v>
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>43.18129348754883</v>
+        <v>43.1812858581543</v>
       </c>
       <c r="C166" t="n">
         <v>44.55816650390625</v>
@@ -4701,11 +4713,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>48.20460891723633</v>
+        <v>48.20461273193359</v>
       </c>
       <c r="C167" t="n">
         <v>49.74166488647461</v>
@@ -4728,11 +4740,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>54.43546676635742</v>
+        <v>54.43547439575195</v>
       </c>
       <c r="C168" t="n">
         <v>56.17119979858398</v>
@@ -4755,11 +4767,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>53.95301818847656</v>
+        <v>53.95303726196289</v>
       </c>
       <c r="C169" t="n">
         <v>55.62294387817383</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>60.18952560424805</v>
+        <v>60.18952941894531</v>
       </c>
       <c r="C170" t="n">
         <v>62.0524787902832</v>
@@ -4809,11 +4821,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>52.59936904907227</v>
+        <v>52.59937286376953</v>
       </c>
       <c r="C171" t="n">
         <v>54.22738647460938</v>
@@ -4836,11 +4848,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.4240608215332</v>
+        <v>38.42405700683594</v>
       </c>
       <c r="C172" t="n">
         <v>39.57403182983398</v>
@@ -4863,7 +4875,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4890,11 +4902,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.79420852661133</v>
+        <v>31.79421043395996</v>
       </c>
       <c r="C174" t="n">
         <v>32.74576568603516</v>
@@ -4917,11 +4929,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>33.10197448730469</v>
+        <v>33.10198211669922</v>
       </c>
       <c r="C175" t="n">
         <v>34.04164123535156</v>
@@ -4944,11 +4956,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>29.41859817504883</v>
+        <v>29.41860389709473</v>
       </c>
       <c r="C176" t="n">
         <v>30.25369834899902</v>
@@ -4971,11 +4983,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>30.72717094421387</v>
+        <v>30.7271671295166</v>
       </c>
       <c r="C177" t="n">
         <v>31.59941482543945</v>
@@ -4998,11 +5010,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>30.24395561218262</v>
+        <v>30.24395370483398</v>
       </c>
       <c r="C178" t="n">
         <v>31.05116081237793</v>
@@ -5025,11 +5037,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>36.02088928222656</v>
+        <v>36.02089309692383</v>
       </c>
       <c r="C179" t="n">
         <v>36.98228073120117</v>
@@ -5054,11 +5066,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>49.41950225830078</v>
+        <v>49.41950607299805</v>
       </c>
       <c r="C180" t="n">
         <v>50.73849487304688</v>
@@ -5083,7 +5095,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5112,7 +5124,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5141,11 +5153,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>60.93228530883789</v>
+        <v>60.93228149414062</v>
       </c>
       <c r="C183" t="n">
         <v>62.50105285644531</v>
@@ -5170,11 +5182,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>63.84614944458008</v>
+        <v>63.84615707397461</v>
       </c>
       <c r="C184" t="n">
         <v>65.44168853759766</v>
@@ -5199,11 +5211,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>63.79751968383789</v>
+        <v>63.79753112792969</v>
       </c>
       <c r="C185" t="n">
         <v>65.39185333251953</v>
@@ -5226,11 +5238,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>68.36838531494141</v>
+        <v>68.36839294433594</v>
       </c>
       <c r="C186" t="n">
         <v>70.07693481445312</v>
@@ -5253,11 +5265,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>65.50063323974609</v>
+        <v>65.50062561035156</v>
       </c>
       <c r="C187" t="n">
         <v>67.08645629882812</v>
@@ -5280,11 +5292,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>63.01881790161133</v>
+        <v>63.0188102722168</v>
       </c>
       <c r="C188" t="n">
         <v>64.54454803466797</v>
@@ -5307,11 +5319,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>64.11981964111328</v>
+        <v>64.11981201171875</v>
       </c>
       <c r="C189" t="n">
         <v>65.67221069335938</v>
@@ -5334,11 +5346,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>62.72082138061523</v>
+        <v>62.72082901000977</v>
       </c>
       <c r="C190" t="n">
         <v>64.18943023681641</v>
@@ -5361,11 +5373,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>63.84093856811523</v>
+        <v>63.84094619750977</v>
       </c>
       <c r="C191" t="n">
         <v>65.33577728271484</v>
@@ -5388,11 +5400,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>57.82637023925781</v>
+        <v>57.82636642456055</v>
       </c>
       <c r="C192" t="n">
         <v>59.18037033081055</v>
@@ -5415,11 +5427,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>57.56017684936523</v>
+        <v>57.56016540527344</v>
       </c>
       <c r="C193" t="n">
         <v>58.85640335083008</v>
@@ -5442,7 +5454,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5469,11 +5481,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.1938362121582</v>
+        <v>58.19382858276367</v>
       </c>
       <c r="C195" t="n">
         <v>59.50434112548828</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>55.80063247680664</v>
+        <v>55.80062866210938</v>
       </c>
       <c r="C196" t="n">
         <v>57.00604248046875</v>
@@ -5523,11 +5535,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>45.46379470825195</v>
+        <v>45.46379089355469</v>
       </c>
       <c r="C197" t="n">
         <v>46.44590759277344</v>
@@ -5550,11 +5562,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>47.74460983276367</v>
+        <v>47.74459838867188</v>
       </c>
       <c r="C198" t="n">
         <v>48.7759895324707</v>
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.87506484985352</v>
+        <v>38.87505722045898</v>
       </c>
       <c r="C199" t="n">
         <v>39.66748428344727</v>
@@ -5604,11 +5616,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>45.12731170654297</v>
+        <v>45.1273193359375</v>
       </c>
       <c r="C200" t="n">
         <v>46.04717636108398</v>
@@ -5631,11 +5643,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>44.84034729003906</v>
+        <v>44.8403434753418</v>
       </c>
       <c r="C201" t="n">
         <v>45.75435638427734</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>37.84736251831055</v>
+        <v>37.84736633300781</v>
       </c>
       <c r="C202" t="n">
         <v>38.57097244262695</v>
@@ -5685,11 +5697,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>47.5674934387207</v>
+        <v>47.56748962402344</v>
       </c>
       <c r="C203" t="n">
         <v>48.4769401550293</v>
@@ -5712,11 +5724,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>52.55593490600586</v>
+        <v>52.55594253540039</v>
       </c>
       <c r="C204" t="n">
         <v>53.56076049804688</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>51.27273178100586</v>
+        <v>51.27273941040039</v>
       </c>
       <c r="C205" t="n">
         <v>52.20258331298828</v>
@@ -5766,11 +5778,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>63.08575820922852</v>
+        <v>63.08576583862305</v>
       </c>
       <c r="C206" t="n">
         <v>64.22985076904297</v>
@@ -5793,7 +5805,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5822,11 +5834,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>75.00732421875</v>
+        <v>75.00731658935547</v>
       </c>
       <c r="C208" t="n">
         <v>76.29689025878906</v>
@@ -5851,11 +5863,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>77.65142059326172</v>
+        <v>77.65141296386719</v>
       </c>
       <c r="C209" t="n">
         <v>78.98643493652344</v>
@@ -5880,11 +5892,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>79.65998077392578</v>
+        <v>79.65996551513672</v>
       </c>
       <c r="C210" t="n">
         <v>81.02952575683594</v>
@@ -5909,11 +5921,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>86.18779754638672</v>
+        <v>86.18781280517578</v>
       </c>
       <c r="C211" t="n">
         <v>87.66959381103516</v>
@@ -5938,7 +5950,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5967,11 +5979,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>89.87120819091797</v>
+        <v>89.8712158203125</v>
       </c>
       <c r="C213" t="n">
         <v>91.34876251220703</v>
@@ -5996,11 +6008,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>86.86363220214844</v>
+        <v>86.86363983154297</v>
       </c>
       <c r="C214" t="n">
         <v>88.22824859619141</v>
@@ -6025,11 +6037,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>85.35502624511719</v>
+        <v>85.35501861572266</v>
       </c>
       <c r="C215" t="n">
         <v>86.69593048095703</v>
@@ -6054,11 +6066,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>95.70322418212891</v>
+        <v>95.70321655273438</v>
       </c>
       <c r="C216" t="n">
         <v>97.20670318603516</v>
@@ -6083,11 +6095,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>100.347053527832</v>
+        <v>100.3470458984375</v>
       </c>
       <c r="C217" t="n">
         <v>101.8595352172852</v>
@@ -6112,11 +6124,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>104.1131286621094</v>
+        <v>104.1131210327148</v>
       </c>
       <c r="C218" t="n">
         <v>105.6823654174805</v>
@@ -6141,11 +6153,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>123.3522872924805</v>
+        <v>123.3522720336914</v>
       </c>
       <c r="C219" t="n">
         <v>125.2114944458008</v>
@@ -6170,11 +6182,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>138.0076599121094</v>
+        <v>138.0076904296875</v>
       </c>
       <c r="C220" t="n">
         <v>140.0877838134766</v>
@@ -6199,11 +6211,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>159.7007751464844</v>
+        <v>159.7007904052734</v>
       </c>
       <c r="C221" t="n">
         <v>161.8200073242188</v>
@@ -6228,7 +6240,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6257,11 +6269,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>156.8881072998047</v>
+        <v>156.8880920410156</v>
       </c>
       <c r="C223" t="n">
         <v>158.9700012207031</v>
@@ -6286,11 +6298,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>168.2553558349609</v>
+        <v>168.2553405761719</v>
       </c>
       <c r="C224" t="n">
         <v>170.1999969482422</v>
@@ -6315,7 +6327,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6344,11 +6356,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>186.7014465332031</v>
+        <v>186.7014617919922</v>
       </c>
       <c r="C226" t="n">
         <v>188.5800018310547</v>
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6402,11 +6414,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>180.3454284667969</v>
+        <v>180.3454132080078</v>
       </c>
       <c r="C228" t="n">
         <v>182.1600036621094</v>
@@ -6431,7 +6443,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6460,11 +6472,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>201.8704986572266</v>
+        <v>201.8704681396484</v>
       </c>
       <c r="C230" t="n">
         <v>203.5700073242188</v>
@@ -6489,11 +6501,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>205.2519989013672</v>
+        <v>205.2520141601562</v>
       </c>
       <c r="C231" t="n">
         <v>206.9799957275391</v>
@@ -6518,7 +6530,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6547,11 +6559,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>200.2292785644531</v>
+        <v>200.2292633056641</v>
       </c>
       <c r="C233" t="n">
         <v>201.5399932861328</v>
@@ -6576,11 +6588,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>244.3106994628906</v>
+        <v>244.3107147216797</v>
       </c>
       <c r="C234" t="n">
         <v>245.9100036621094</v>
@@ -6605,11 +6617,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>255.7160949707031</v>
+        <v>255.716064453125</v>
       </c>
       <c r="C235" t="n">
         <v>257.3900146484375</v>
@@ -6634,7 +6646,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6663,7 +6675,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6692,7 +6704,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6721,11 +6733,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>307.7645568847656</v>
+        <v>307.7645874023438</v>
       </c>
       <c r="C239" t="n">
         <v>308.9500122070312</v>
@@ -6750,11 +6762,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>297.3049011230469</v>
+        <v>297.3048706054688</v>
       </c>
       <c r="C240" t="n">
         <v>298.4500122070312</v>
@@ -6779,7 +6791,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6808,7 +6820,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6837,11 +6849,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>341.3367004394531</v>
+        <v>341.336669921875</v>
       </c>
       <c r="C243" t="n">
         <v>342.260009765625</v>
@@ -6866,7 +6878,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6895,7 +6907,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6924,7 +6936,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6953,7 +6965,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6982,7 +6994,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7011,7 +7023,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7040,32 +7052,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>319.7999877929688</v>
+        <v>319.7799987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>319.7999877929688</v>
+        <v>319.7799987792969</v>
       </c>
       <c r="D250" t="n">
-        <v>69216200</v>
+        <v>72942500</v>
       </c>
       <c r="E250" t="n">
         <v>8.489999999999998</v>
       </c>
       <c r="F250" t="n">
-        <v>37.66784308515534</v>
+        <v>37.66548866658385</v>
       </c>
       <c r="G250" t="n">
         <v>1037562513</v>
       </c>
       <c r="H250" t="n">
-        <v>331812478991.842</v>
+        <v>331791739140.5842</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06671039010446593</v>
+        <v>0.07030178816801566</v>
       </c>
     </row>
   </sheetData>
@@ -7097,75 +7109,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7201,13 +7213,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7243,13 +7255,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7285,13 +7297,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7402,7 +7414,7 @@
       <c r="I7" t="n">
         <v>4.840361754260202</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7415,13 +7427,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7448,7 +7460,7 @@
       <c r="I8" t="n">
         <v>4.409042390019194</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7461,13 +7473,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7494,7 +7506,7 @@
       <c r="I9" t="n">
         <v>4.60073988523742</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I10" t="n">
         <v>4.361118016214637</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I11" t="n">
         <v>5.032059249478428</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I12" t="n">
         <v>5.703000482742219</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I13" t="n">
         <v>6.038471099374114</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="K13" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I14" t="n">
         <v>6.230168594592339</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K14" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I15" t="n">
         <v>5.894697977960444</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I16" t="n">
         <v>5.798849230351331</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K16" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I17" t="n">
         <v>5.511302987523992</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="K17" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I18" t="n">
         <v>6.038471099374114</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I19" t="n">
         <v>6.182244220787783</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K19" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I20" t="n">
         <v>6.421866089810565</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I21" t="n">
         <v>6.469790463615121</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K21" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I22" t="n">
         <v>6.373941716006009</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K22" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I23" t="n">
         <v>6.08639547317867</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I24" t="n">
         <v>5.894697977960444</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="K24" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I25" t="n">
         <v>6.134319846983226</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I26" t="n">
         <v>6.326017342201451</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K26" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I27" t="n">
         <v>7.236580444488025</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I28" t="n">
         <v>-0.6709412332637914</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K28" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I29" t="n">
         <v>-2.971311175882501</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I30" t="n">
         <v>-3.450554913928066</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K30" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I31" t="n">
         <v>-2.827538054468832</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I32" t="n">
         <v>3.594328035341734</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I33" t="n">
         <v>5.655076108937662</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K33" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I34" t="n">
         <v>5.511302987523992</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K34" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I35" t="n">
         <v>4.313193642410081</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K35" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I36" t="n">
         <v>4.696588632846532</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K36" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I37" t="n">
         <v>3.881874278169072</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K37" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I38" t="n">
         <v>3.833949904364516</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="K38" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I39" t="n">
         <v>-3.450554913928064</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K39" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I40" t="n">
         <v>-4.45696676382375</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K40" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I41" t="n">
         <v>-4.744513006651088</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I42" t="n">
         <v>-18.30711079334057</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K42" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I43" t="n">
         <v>-12.54276711212852</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K43" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I44" t="n">
         <v>-9.878171928595178</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K44" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I45" t="n">
         <v>-10.26348389398381</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I46" t="n">
         <v>-3.090163622917801</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K46" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I47" t="n">
         <v>-3.14000497167454</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="K47" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I48" t="n">
         <v>-1.644764508972379</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I49" t="n">
         <v>-2.890798227890847</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I50" t="n">
         <v>1.794288555242593</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I51" t="n">
         <v>2.890798227890845</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K51" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I52" t="n">
         <v>-2.242860694053243</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K52" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I53" t="n">
         <v>-1.644764508972378</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K53" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I54" t="n">
         <v>-0.2741274181620631</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K54" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I55" t="n">
         <v>-3.881395034431028</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I56" t="n">
         <v>-2.853417216323292</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K56" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I57" t="n">
         <v>-2.641591484107153</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="K57" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I58" t="n">
         <v>-3.445283232809564</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K58" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I59" t="n">
         <v>0.3067298904175635</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I60" t="n">
         <v>6.278664226932644</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K60" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I61" t="n">
         <v>6.748655685371501</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K61" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I62" t="n">
         <v>7.063048683160414</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K62" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I63" t="n">
         <v>6.679968076616121</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K63" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I64" t="n">
         <v>2.71482043096568</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K64" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I65" t="n">
         <v>3.880782122905026</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="K65" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I66" t="n">
         <v>5.397222665602552</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K66" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I67" t="n">
         <v>5.989999999999998</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="K67" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I68" t="n">
         <v>6.429999999999998</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K68" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I69" t="n">
         <v>7.169999999999998</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="K69" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I70" t="n">
         <v>7.489999999999998</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K70" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I71" t="n">
         <v>8.139999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K71" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I72" t="n">
         <v>8.119999999999997</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="K72" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I73" t="n">
         <v>8.489999999999998</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="K73" t="n">
@@ -10475,52 +10487,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="C2" t="n">
@@ -10549,10 +10561,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="C3" t="n">
@@ -10581,10 +10593,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C4" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40354</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="C6" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40445</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="C10" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C11" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40942</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="C14" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C15" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C16" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="C21" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C22" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C23" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C25" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C27" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C28" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C30" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C31" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C32" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C33" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="C35" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C36" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C37" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C39" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C41" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="C44" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C48" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C51" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C53" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="C54" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C55" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C57" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C59" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45306</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C60" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C61" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="C62" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C63" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45672</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="C64" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="C66" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C67" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46037</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C68" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="C70" t="n">
@@ -12743,12 +12755,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GE.xlsx
+++ b/salidas/empresas/GE.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>96.39454650878906</v>
+        <v>96.39453887939453</v>
       </c>
       <c r="C2" t="n">
         <v>156.9523315429688</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>97.47212219238281</v>
+        <v>97.47214508056641</v>
       </c>
       <c r="C3" t="n">
         <v>157.5274200439453</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>103.1360015869141</v>
+        <v>103.1360321044922</v>
       </c>
       <c r="C4" t="n">
         <v>166.6809692382812</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>102.5726013183594</v>
+        <v>102.5725631713867</v>
       </c>
       <c r="C5" t="n">
         <v>165.7704162597656</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>101.5939865112305</v>
+        <v>101.5940093994141</v>
       </c>
       <c r="C6" t="n">
         <v>164.1889038085938</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>98.47017669677734</v>
+        <v>98.47016143798828</v>
       </c>
       <c r="C7" t="n">
         <v>157.958740234375</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>97.66356658935547</v>
+        <v>97.66349792480469</v>
       </c>
       <c r="C8" t="n">
         <v>156.6647796630859</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>101.7564849853516</v>
+        <v>101.7564697265625</v>
       </c>
       <c r="C9" t="n">
         <v>163.2304229736328</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>106.2193374633789</v>
+        <v>106.2193069458008</v>
       </c>
       <c r="C10" t="n">
         <v>169.1730346679688</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>105.6475677490234</v>
+        <v>105.6476135253906</v>
       </c>
       <c r="C11" t="n">
         <v>168.2624816894531</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>106.1591796875</v>
+        <v>106.1591644287109</v>
       </c>
       <c r="C12" t="n">
         <v>169.0771942138672</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>112.7944717407227</v>
+        <v>112.7945022583008</v>
       </c>
       <c r="C13" t="n">
         <v>178.3265991210938</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>109.2781066894531</v>
+        <v>109.2781829833984</v>
       </c>
       <c r="C14" t="n">
         <v>172.7673645019531</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>106.6540832519531</v>
+        <v>106.6540908813477</v>
       </c>
       <c r="C15" t="n">
         <v>167.3039855957031</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>112.6115798950195</v>
+        <v>112.6115875244141</v>
       </c>
       <c r="C17" t="n">
         <v>176.6492462158203</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>114.8112411499023</v>
+        <v>114.8112335205078</v>
       </c>
       <c r="C18" t="n">
         <v>180.0997924804688</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>117.7940521240234</v>
+        <v>117.7940216064453</v>
       </c>
       <c r="C19" t="n">
         <v>183.4544982910156</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>119.2709655761719</v>
+        <v>119.2710571289062</v>
       </c>
       <c r="C20" t="n">
         <v>185.7548675537109</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>119.6095657348633</v>
+        <v>119.6095581054688</v>
       </c>
       <c r="C21" t="n">
         <v>186.2820434570312</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>128.2545471191406</v>
+        <v>128.2545166015625</v>
       </c>
       <c r="C22" t="n">
         <v>198.4069061279297</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>127.5109710693359</v>
+        <v>127.5110092163086</v>
       </c>
       <c r="C23" t="n">
         <v>197.2567291259766</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>118.6199569702148</v>
+        <v>118.6200103759766</v>
       </c>
       <c r="C24" t="n">
         <v>183.5024261474609</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>115.8222732543945</v>
+        <v>115.822265625</v>
       </c>
       <c r="C25" t="n">
         <v>177.6556549072266</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>110.4795227050781</v>
+        <v>110.4795074462891</v>
       </c>
       <c r="C26" t="n">
         <v>169.4605865478516</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>104.4859466552734</v>
+        <v>104.4859924316406</v>
       </c>
       <c r="C27" t="n">
         <v>158.8213806152344</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>116.6876068115234</v>
+        <v>116.6875915527344</v>
       </c>
       <c r="C28" t="n">
         <v>177.3681030273438</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>103.0987396240234</v>
+        <v>103.0987243652344</v>
       </c>
       <c r="C29" t="n">
         <v>156.7127075195312</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>96.8560791015625</v>
+        <v>96.85607147216797</v>
       </c>
       <c r="C30" t="n">
         <v>147.2236785888672</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>85.08499145507812</v>
+        <v>85.08502960205078</v>
       </c>
       <c r="C31" t="n">
         <v>127.91015625</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>90.18564605712891</v>
+        <v>90.18563842773438</v>
       </c>
       <c r="C32" t="n">
         <v>135.5780487060547</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>89.57994842529297</v>
+        <v>89.57993316650391</v>
       </c>
       <c r="C33" t="n">
         <v>134.6674957275391</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>82.38328552246094</v>
+        <v>82.38325500488281</v>
       </c>
       <c r="C34" t="n">
         <v>122.2071533203125</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>63.03126907348633</v>
+        <v>63.0312614440918</v>
       </c>
       <c r="C35" t="n">
         <v>93.50045013427734</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>55.47138214111328</v>
+        <v>55.47140884399414</v>
       </c>
       <c r="C36" t="n">
         <v>82.28614807128906</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>53.34410858154297</v>
+        <v>53.34409713745117</v>
       </c>
       <c r="C37" t="n">
         <v>77.63748931884766</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>39.94222259521484</v>
+        <v>39.94223022460938</v>
       </c>
       <c r="C38" t="n">
         <v>58.13226318359375</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.84550476074219</v>
+        <v>28.84551048278809</v>
       </c>
       <c r="C39" t="n">
         <v>40.78364181518555</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>34.26888275146484</v>
+        <v>34.26887512207031</v>
       </c>
       <c r="C40" t="n">
         <v>48.45154190063477</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>42.87846755981445</v>
+        <v>42.87847137451172</v>
       </c>
       <c r="C41" t="n">
         <v>60.62433242797852</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>45.69183349609375</v>
+        <v>45.69185256958008</v>
       </c>
       <c r="C42" t="n">
         <v>64.60205841064453</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>40.05310821533203</v>
+        <v>40.0531005859375</v>
       </c>
       <c r="C43" t="n">
         <v>56.16736602783203</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>45.79450988769531</v>
+        <v>45.79449844360352</v>
       </c>
       <c r="C44" t="n">
         <v>64.21865844726562</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>47.50326919555664</v>
+        <v>47.50325775146484</v>
       </c>
       <c r="C45" t="n">
         <v>66.61488342285156</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>56.44740676879883</v>
+        <v>56.44738388061523</v>
       </c>
       <c r="C46" t="n">
         <v>78.69181823730469</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>55.07230377197266</v>
+        <v>55.07232284545898</v>
       </c>
       <c r="C48" t="n">
         <v>76.77484893798828</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>52.35091018676758</v>
+        <v>52.35092544555664</v>
       </c>
       <c r="C49" t="n">
         <v>72.50957489013672</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>55.63798904418945</v>
+        <v>55.63801193237305</v>
       </c>
       <c r="C50" t="n">
         <v>77.06239318847656</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>55.91567611694336</v>
+        <v>55.91565322875977</v>
       </c>
       <c r="C51" t="n">
         <v>76.96654510498047</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>63.36645126342773</v>
+        <v>63.36643981933594</v>
       </c>
       <c r="C52" t="n">
         <v>87.22235870361328</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>65.66434478759766</v>
+        <v>65.66432952880859</v>
       </c>
       <c r="C53" t="n">
         <v>90.38536834716797</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>56.92534637451172</v>
+        <v>56.92533874511719</v>
       </c>
       <c r="C54" t="n">
         <v>78.35635375976562</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>56.48093032836914</v>
+        <v>56.48089599609375</v>
       </c>
       <c r="C56" t="n">
         <v>77.25408935546875</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>50.73470687866211</v>
+        <v>50.73471832275391</v>
       </c>
       <c r="C57" t="n">
         <v>69.39449310302734</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>57.35759735107422</v>
+        <v>57.35764694213867</v>
       </c>
       <c r="C58" t="n">
         <v>77.87710571289062</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>56.54581451416016</v>
+        <v>56.54580688476562</v>
       </c>
       <c r="C59" t="n">
         <v>76.77484893798828</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>55.87514495849609</v>
+        <v>55.87513732910156</v>
       </c>
       <c r="C60" t="n">
         <v>75.86428070068359</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>65.06710815429688</v>
+        <v>65.067138671875</v>
       </c>
       <c r="C61" t="n">
         <v>87.65367889404297</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>71.64852142333984</v>
+        <v>71.64855194091797</v>
       </c>
       <c r="C62" t="n">
         <v>96.51969146728516</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>74.93843078613281</v>
+        <v>74.93844604492188</v>
       </c>
       <c r="C63" t="n">
         <v>100.2577896118164</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>71.82197570800781</v>
+        <v>71.82198333740234</v>
       </c>
       <c r="C64" t="n">
         <v>96.08837127685547</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>73.25485229492188</v>
+        <v>73.25479888916016</v>
       </c>
       <c r="C65" t="n">
         <v>98.00534057617188</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>70.35330200195312</v>
+        <v>70.35330963134766</v>
       </c>
       <c r="C66" t="n">
         <v>94.12346649169922</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>68.11482238769531</v>
+        <v>68.11479949951172</v>
       </c>
       <c r="C67" t="n">
         <v>90.38536834716797</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>64.68381500244141</v>
+        <v>64.68379211425781</v>
       </c>
       <c r="C68" t="n">
         <v>85.83255004882812</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>58.9052619934082</v>
+        <v>58.90525436401367</v>
       </c>
       <c r="C69" t="n">
         <v>78.16465759277344</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>55.49578857421875</v>
+        <v>55.49578475952148</v>
       </c>
       <c r="C70" t="n">
         <v>72.94089508056641</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>60.92869567871094</v>
+        <v>60.92866516113281</v>
       </c>
       <c r="C71" t="n">
         <v>80.08162689208984</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>58.0117073059082</v>
+        <v>58.01167297363281</v>
       </c>
       <c r="C72" t="n">
         <v>76.2476806640625</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>65.93779754638672</v>
+        <v>65.93780517578125</v>
       </c>
       <c r="C73" t="n">
         <v>85.83255004882812</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>68.88311004638672</v>
+        <v>68.88313293457031</v>
       </c>
       <c r="C74" t="n">
         <v>89.66650390625</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>70.75517272949219</v>
+        <v>70.75520324707031</v>
       </c>
       <c r="C75" t="n">
         <v>91.29592895507812</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>74.54365539550781</v>
+        <v>74.54368591308594</v>
       </c>
       <c r="C76" t="n">
         <v>96.18421936035156</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>72.72373199462891</v>
+        <v>72.72374725341797</v>
       </c>
       <c r="C77" t="n">
         <v>93.83592224121094</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>70.90376281738281</v>
+        <v>70.90380096435547</v>
       </c>
       <c r="C78" t="n">
         <v>91.48763275146484</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>77.94414520263672</v>
+        <v>77.94411468505859</v>
       </c>
       <c r="C80" t="n">
         <v>99.44307708740234</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>77.79383850097656</v>
+        <v>77.79385375976562</v>
       </c>
       <c r="C81" t="n">
         <v>99.25138092041016</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>85.95802307128906</v>
+        <v>85.95803833007812</v>
       </c>
       <c r="C82" t="n">
         <v>108.8362503051758</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>79.71276092529297</v>
+        <v>79.71273803710938</v>
       </c>
       <c r="C83" t="n">
         <v>100.9287338256836</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>79.97763824462891</v>
+        <v>79.97766876220703</v>
       </c>
       <c r="C84" t="n">
         <v>101.2641983032227</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>80.17282867431641</v>
+        <v>80.17279815673828</v>
       </c>
       <c r="C85" t="n">
         <v>100.59326171875</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>85.10002136230469</v>
+        <v>85.10004425048828</v>
       </c>
       <c r="C86" t="n">
         <v>106.775505065918</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>89.41616058349609</v>
+        <v>89.41616821289062</v>
       </c>
       <c r="C87" t="n">
         <v>111.2803955078125</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>89.03107452392578</v>
+        <v>89.03108215332031</v>
       </c>
       <c r="C88" t="n">
         <v>110.801155090332</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>85.83489990234375</v>
+        <v>85.83489227294922</v>
       </c>
       <c r="C89" t="n">
         <v>106.8234252929688</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>89.80125427246094</v>
+        <v>89.80126190185547</v>
       </c>
       <c r="C90" t="n">
         <v>111.7596435546875</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>90.01386260986328</v>
+        <v>90.01385498046875</v>
       </c>
       <c r="C91" t="n">
         <v>111.1366195678711</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>94.59410095214844</v>
+        <v>94.5941162109375</v>
       </c>
       <c r="C92" t="n">
         <v>116.7917022705078</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>89.81974792480469</v>
+        <v>89.81975555419922</v>
       </c>
       <c r="C93" t="n">
         <v>110.8970031738281</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>93.44512176513672</v>
+        <v>93.44513702392578</v>
       </c>
       <c r="C94" t="n">
         <v>114.491325378418</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>102.2459716796875</v>
+        <v>102.2459487915039</v>
       </c>
       <c r="C95" t="n">
         <v>125.2743148803711</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>104.279899597168</v>
+        <v>104.2799224853516</v>
       </c>
       <c r="C96" t="n">
         <v>127.7663803100586</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>110.5257797241211</v>
+        <v>110.5257186889648</v>
       </c>
       <c r="C97" t="n">
         <v>134.3320159912109</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>99.0906982421875</v>
+        <v>99.09067535400391</v>
       </c>
       <c r="C98" t="n">
         <v>120.433952331543</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>101.308837890625</v>
+        <v>101.3088226318359</v>
       </c>
       <c r="C99" t="n">
         <v>122.0633773803711</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>102.9794006347656</v>
+        <v>102.9794082641602</v>
       </c>
       <c r="C100" t="n">
         <v>124.0762023925781</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>106.9569778442383</v>
+        <v>106.9569396972656</v>
       </c>
       <c r="C101" t="n">
         <v>128.8686370849609</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>106.5592346191406</v>
+        <v>106.5592422485352</v>
       </c>
       <c r="C102" t="n">
         <v>128.389404296875</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>105.392936706543</v>
+        <v>105.3929214477539</v>
       </c>
       <c r="C103" t="n">
         <v>125.9452514648438</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>100.8611831665039</v>
+        <v>100.8611907958984</v>
       </c>
       <c r="C104" t="n">
         <v>120.5298004150391</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>104.1898345947266</v>
+        <v>104.189811706543</v>
       </c>
       <c r="C105" t="n">
         <v>124.5075225830078</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>103.6137924194336</v>
+        <v>103.6138153076172</v>
       </c>
       <c r="C106" t="n">
         <v>122.7822494506836</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>104.3821868896484</v>
+        <v>104.3822021484375</v>
       </c>
       <c r="C107" t="n">
         <v>123.6928100585938</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>107.1323089599609</v>
+        <v>107.1322631835938</v>
       </c>
       <c r="C108" t="n">
         <v>126.9516677856445</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>103.1604766845703</v>
+        <v>103.1604614257812</v>
       </c>
       <c r="C109" t="n">
         <v>121.1048965454102</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>97.52686309814453</v>
+        <v>97.52684783935547</v>
       </c>
       <c r="C110" t="n">
         <v>114.491325378418</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>107.075080871582</v>
+        <v>107.0750885009766</v>
       </c>
       <c r="C111" t="n">
         <v>124.5554504394531</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>102.2136306762695</v>
+        <v>102.2136383056641</v>
       </c>
       <c r="C112" t="n">
         <v>118.9003677368164</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>112.348518371582</v>
+        <v>112.348503112793</v>
       </c>
       <c r="C114" t="n">
         <v>130.6897735595703</v>
@@ -3271,7 +3271,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>110.3956985473633</v>
+        <v>110.3956832885742</v>
       </c>
       <c r="C115" t="n">
         <v>127.3350601196289</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>103.1245956420898</v>
+        <v>103.1246566772461</v>
       </c>
       <c r="C117" t="n">
         <v>118.9482955932617</v>
@@ -3352,7 +3352,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>105.7243728637695</v>
+        <v>105.7243804931641</v>
       </c>
       <c r="C118" t="n">
         <v>120.8652725219727</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>121.2350845336914</v>
+        <v>121.2350921630859</v>
       </c>
       <c r="C119" t="n">
         <v>138.5972900390625</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>125.5109329223633</v>
+        <v>125.5110168457031</v>
       </c>
       <c r="C120" t="n">
         <v>143.4855804443359</v>
@@ -3460,7 +3460,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>122.9021148681641</v>
+        <v>122.902099609375</v>
       </c>
       <c r="C122" t="n">
         <v>139.4599304199219</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>124.0562896728516</v>
+        <v>124.0562973022461</v>
       </c>
       <c r="C123" t="n">
         <v>139.6516265869141</v>
@@ -3568,7 +3568,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>128.6966705322266</v>
+        <v>128.6967010498047</v>
       </c>
       <c r="C126" t="n">
         <v>144.8753814697266</v>
@@ -3597,7 +3597,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>135.0335388183594</v>
+        <v>135.0335540771484</v>
       </c>
       <c r="C127" t="n">
         <v>150.8659362792969</v>
@@ -3626,7 +3626,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>133.5751037597656</v>
+        <v>133.5751190185547</v>
       </c>
       <c r="C128" t="n">
         <v>149.2364959716797</v>
@@ -3655,7 +3655,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>134.0040435791016</v>
+        <v>134.0040893554688</v>
       </c>
       <c r="C129" t="n">
         <v>149.7157440185547</v>
@@ -3684,7 +3684,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>128.0466918945312</v>
+        <v>128.0466461181641</v>
       </c>
       <c r="C130" t="n">
         <v>141.9519958496094</v>
@@ -3713,7 +3713,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>125.7987442016602</v>
+        <v>125.7987594604492</v>
       </c>
       <c r="C131" t="n">
         <v>139.4599304199219</v>
@@ -3742,7 +3742,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>132.9748382568359</v>
+        <v>132.9749145507812</v>
       </c>
       <c r="C132" t="n">
         <v>147.4153747558594</v>
@@ -3771,7 +3771,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>137.6342926025391</v>
+        <v>137.6343078613281</v>
       </c>
       <c r="C133" t="n">
         <v>151.4410247802734</v>
@@ -3800,7 +3800,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>129.3587799072266</v>
+        <v>129.3587951660156</v>
       </c>
       <c r="C134" t="n">
         <v>142.3353881835938</v>
@@ -3829,7 +3829,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>130.8734893798828</v>
+        <v>130.8735046386719</v>
       </c>
       <c r="C135" t="n">
         <v>142.8625640869141</v>
@@ -3887,7 +3887,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>127.2734909057617</v>
+        <v>127.2734603881836</v>
       </c>
       <c r="C137" t="n">
         <v>138.9327545166016</v>
@@ -3916,7 +3916,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>120.2051849365234</v>
+        <v>120.2051773071289</v>
       </c>
       <c r="C138" t="n">
         <v>131.2169342041016</v>
@@ -3945,7 +3945,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>119.5811157226562</v>
+        <v>119.5811080932617</v>
       </c>
       <c r="C139" t="n">
         <v>129.4437408447266</v>
@@ -3974,7 +3974,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>113.3828811645508</v>
+        <v>113.3828964233398</v>
       </c>
       <c r="C140" t="n">
         <v>122.7343215942383</v>
@@ -4003,7 +4003,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>108.6899871826172</v>
+        <v>108.6899642944336</v>
       </c>
       <c r="C141" t="n">
         <v>117.6543350219727</v>
@@ -4032,7 +4032,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>108.1214981079102</v>
+        <v>108.1214828491211</v>
       </c>
       <c r="C142" t="n">
         <v>115.8811340332031</v>
@@ -4061,7 +4061,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>90.14598083496094</v>
+        <v>90.14594268798828</v>
       </c>
       <c r="C143" t="n">
         <v>96.61553955078125</v>
@@ -4090,7 +4090,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>81.78423309326172</v>
+        <v>81.78422546386719</v>
       </c>
       <c r="C144" t="n">
         <v>87.65367889404297</v>
@@ -4119,7 +4119,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.56686401367188</v>
+        <v>78.56687927246094</v>
       </c>
       <c r="C145" t="n">
         <v>83.62802886962891</v>
@@ -4148,7 +4148,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>72.80380249023438</v>
+        <v>72.80381011962891</v>
       </c>
       <c r="C146" t="n">
         <v>77.49371337890625</v>
@@ -4177,7 +4177,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>64.05462646484375</v>
+        <v>64.05461120605469</v>
       </c>
       <c r="C147" t="n">
         <v>67.62129211425781</v>
@@ -4204,7 +4204,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>61.19462966918945</v>
+        <v>61.19461822509766</v>
       </c>
       <c r="C148" t="n">
         <v>64.60205841064453</v>
@@ -4231,7 +4231,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>63.87302398681641</v>
+        <v>63.87301254272461</v>
       </c>
       <c r="C149" t="n">
         <v>67.42959594726562</v>
@@ -4258,7 +4258,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>63.91843032836914</v>
+        <v>63.91841125488281</v>
       </c>
       <c r="C150" t="n">
         <v>67.47751617431641</v>
@@ -4285,7 +4285,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>62.33316040039062</v>
+        <v>62.33316421508789</v>
       </c>
       <c r="C151" t="n">
         <v>65.22507476806641</v>
@@ -4312,7 +4312,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>62.42475891113281</v>
+        <v>62.42476272583008</v>
       </c>
       <c r="C152" t="n">
         <v>65.3209228515625</v>
@@ -4339,7 +4339,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>59.26459121704102</v>
+        <v>59.26459884643555</v>
       </c>
       <c r="C153" t="n">
         <v>62.01414108276367</v>
@@ -4366,7 +4366,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>52.20053482055664</v>
+        <v>52.20052719116211</v>
       </c>
       <c r="C154" t="n">
         <v>54.10661697387695</v>
@@ -4393,7 +4393,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>46.69843292236328</v>
+        <v>46.69843673706055</v>
       </c>
       <c r="C155" t="n">
         <v>48.40361785888672</v>
@@ -4447,7 +4447,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>35.04884719848633</v>
+        <v>35.04883575439453</v>
       </c>
       <c r="C157" t="n">
         <v>36.27875137329102</v>
@@ -4474,7 +4474,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>47.04044723510742</v>
+        <v>47.04045867919922</v>
       </c>
       <c r="C158" t="n">
         <v>48.691162109375</v>
@@ -4501,7 +4501,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>50.02956390380859</v>
+        <v>50.02956771850586</v>
       </c>
       <c r="C159" t="n">
         <v>51.78516006469727</v>
@@ -4528,7 +4528,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.15446472167969</v>
+        <v>48.15446090698242</v>
       </c>
       <c r="C160" t="n">
         <v>49.79150772094727</v>
@@ -4555,7 +4555,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>49.02210998535156</v>
+        <v>49.0221061706543</v>
       </c>
       <c r="C161" t="n">
         <v>50.68865203857422</v>
@@ -4582,7 +4582,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.50331115722656</v>
+        <v>45.50329971313477</v>
       </c>
       <c r="C162" t="n">
         <v>47.05023193359375</v>
@@ -4609,7 +4609,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>50.6614990234375</v>
+        <v>50.66151428222656</v>
       </c>
       <c r="C163" t="n">
         <v>52.33341598510742</v>
@@ -4690,7 +4690,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>43.1812858581543</v>
+        <v>43.18127822875977</v>
       </c>
       <c r="C166" t="n">
         <v>44.55816650390625</v>
@@ -4744,7 +4744,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>54.43547439575195</v>
+        <v>54.43546295166016</v>
       </c>
       <c r="C168" t="n">
         <v>56.17119979858398</v>
@@ -4771,7 +4771,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>53.95303726196289</v>
+        <v>53.95302963256836</v>
       </c>
       <c r="C169" t="n">
         <v>55.62294387817383</v>
@@ -4798,7 +4798,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>60.18952941894531</v>
+        <v>60.18953323364258</v>
       </c>
       <c r="C170" t="n">
         <v>62.0524787902832</v>
@@ -4825,7 +4825,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>52.59937286376953</v>
+        <v>52.59935760498047</v>
       </c>
       <c r="C171" t="n">
         <v>54.22738647460938</v>
@@ -4852,7 +4852,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.42405700683594</v>
+        <v>38.42404937744141</v>
       </c>
       <c r="C172" t="n">
         <v>39.57403182983398</v>
@@ -4879,7 +4879,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>32.90725326538086</v>
+        <v>32.90724563598633</v>
       </c>
       <c r="C173" t="n">
         <v>33.89211654663086</v>
@@ -4906,7 +4906,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.79421043395996</v>
+        <v>31.79420852661133</v>
       </c>
       <c r="C174" t="n">
         <v>32.74576568603516</v>
@@ -4933,7 +4933,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>33.10198211669922</v>
+        <v>33.10198593139648</v>
       </c>
       <c r="C175" t="n">
         <v>34.04164123535156</v>
@@ -4960,7 +4960,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>29.41860389709473</v>
+        <v>29.41860198974609</v>
       </c>
       <c r="C176" t="n">
         <v>30.25369834899902</v>
@@ -5014,7 +5014,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>30.24395370483398</v>
+        <v>30.24395751953125</v>
       </c>
       <c r="C178" t="n">
         <v>31.05116081237793</v>
@@ -5041,7 +5041,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>36.02089309692383</v>
+        <v>36.0208854675293</v>
       </c>
       <c r="C179" t="n">
         <v>36.98228073120117</v>
@@ -5070,7 +5070,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>49.41950607299805</v>
+        <v>49.41949081420898</v>
       </c>
       <c r="C180" t="n">
         <v>50.73849487304688</v>
@@ -5099,7 +5099,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>52.47755432128906</v>
+        <v>52.47756576538086</v>
       </c>
       <c r="C181" t="n">
         <v>53.82865524291992</v>
@@ -5128,7 +5128,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>51.89447784423828</v>
+        <v>51.89447402954102</v>
       </c>
       <c r="C182" t="n">
         <v>53.23056030273438</v>
@@ -5157,7 +5157,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>60.93228149414062</v>
+        <v>60.93228530883789</v>
       </c>
       <c r="C183" t="n">
         <v>62.50105285644531</v>
@@ -5186,7 +5186,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>63.84615707397461</v>
+        <v>63.84616088867188</v>
       </c>
       <c r="C184" t="n">
         <v>65.44168853759766</v>
@@ -5215,7 +5215,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>63.79753112792969</v>
+        <v>63.79754257202148</v>
       </c>
       <c r="C185" t="n">
         <v>65.39185333251953</v>
@@ -5242,7 +5242,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>68.36839294433594</v>
+        <v>68.36840057373047</v>
       </c>
       <c r="C186" t="n">
         <v>70.07693481445312</v>
@@ -5269,7 +5269,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>65.50062561035156</v>
+        <v>65.50063323974609</v>
       </c>
       <c r="C187" t="n">
         <v>67.08645629882812</v>
@@ -5296,7 +5296,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>63.0188102722168</v>
+        <v>63.01881408691406</v>
       </c>
       <c r="C188" t="n">
         <v>64.54454803466797</v>
@@ -5323,7 +5323,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>64.11981201171875</v>
+        <v>64.11982727050781</v>
       </c>
       <c r="C189" t="n">
         <v>65.67221069335938</v>
@@ -5350,7 +5350,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>62.72082901000977</v>
+        <v>62.72081756591797</v>
       </c>
       <c r="C190" t="n">
         <v>64.18943023681641</v>
@@ -5377,7 +5377,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>63.84094619750977</v>
+        <v>63.84093475341797</v>
       </c>
       <c r="C191" t="n">
         <v>65.33577728271484</v>
@@ -5431,7 +5431,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>57.56016540527344</v>
+        <v>57.56015396118164</v>
       </c>
       <c r="C193" t="n">
         <v>58.85640335083008</v>
@@ -5485,7 +5485,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.19382858276367</v>
+        <v>58.19383239746094</v>
       </c>
       <c r="C195" t="n">
         <v>59.50434112548828</v>
@@ -5539,7 +5539,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>45.46379089355469</v>
+        <v>45.46379470825195</v>
       </c>
       <c r="C197" t="n">
         <v>46.44590759277344</v>
@@ -5566,7 +5566,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>47.74459838867188</v>
+        <v>47.74459457397461</v>
       </c>
       <c r="C198" t="n">
         <v>48.7759895324707</v>
@@ -5593,7 +5593,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.87505722045898</v>
+        <v>38.87506866455078</v>
       </c>
       <c r="C199" t="n">
         <v>39.66748428344727</v>
@@ -5674,7 +5674,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>37.84736633300781</v>
+        <v>37.84736251831055</v>
       </c>
       <c r="C202" t="n">
         <v>38.57097244262695</v>
@@ -5701,7 +5701,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>47.56748962402344</v>
+        <v>47.56749725341797</v>
       </c>
       <c r="C203" t="n">
         <v>48.4769401550293</v>
@@ -5755,7 +5755,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>51.27273941040039</v>
+        <v>51.27273178100586</v>
       </c>
       <c r="C205" t="n">
         <v>52.20258331298828</v>
@@ -5782,7 +5782,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>63.08576583862305</v>
+        <v>63.08576202392578</v>
       </c>
       <c r="C206" t="n">
         <v>64.22985076904297</v>
@@ -5809,7 +5809,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>66.40152740478516</v>
+        <v>66.40153503417969</v>
       </c>
       <c r="C207" t="n">
         <v>67.60574340820312</v>
@@ -5838,7 +5838,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>75.00731658935547</v>
+        <v>75.00733184814453</v>
       </c>
       <c r="C208" t="n">
         <v>76.29689025878906</v>
@@ -5867,7 +5867,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>77.65141296386719</v>
+        <v>77.65140533447266</v>
       </c>
       <c r="C209" t="n">
         <v>78.98643493652344</v>
@@ -5896,7 +5896,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>79.65996551513672</v>
+        <v>79.65998077392578</v>
       </c>
       <c r="C210" t="n">
         <v>81.02952575683594</v>
@@ -5925,7 +5925,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>86.18781280517578</v>
+        <v>86.18782043457031</v>
       </c>
       <c r="C211" t="n">
         <v>87.66959381103516</v>
@@ -5983,7 +5983,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>89.8712158203125</v>
+        <v>89.87120819091797</v>
       </c>
       <c r="C213" t="n">
         <v>91.34876251220703</v>
@@ -6041,7 +6041,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>85.35501861572266</v>
+        <v>85.35501098632812</v>
       </c>
       <c r="C215" t="n">
         <v>86.69593048095703</v>
@@ -6070,7 +6070,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>95.70321655273438</v>
+        <v>95.70320892333984</v>
       </c>
       <c r="C216" t="n">
         <v>97.20670318603516</v>
@@ -6099,7 +6099,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>100.3470458984375</v>
+        <v>100.3470687866211</v>
       </c>
       <c r="C217" t="n">
         <v>101.8595352172852</v>
@@ -6128,7 +6128,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>104.1131210327148</v>
+        <v>104.1131362915039</v>
       </c>
       <c r="C218" t="n">
         <v>105.6823654174805</v>
@@ -6215,7 +6215,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>159.7007904052734</v>
+        <v>159.7007751464844</v>
       </c>
       <c r="C221" t="n">
         <v>161.8200073242188</v>
@@ -6273,7 +6273,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>156.8880920410156</v>
+        <v>156.8881072998047</v>
       </c>
       <c r="C223" t="n">
         <v>158.9700012207031</v>
@@ -6302,7 +6302,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>168.2553405761719</v>
+        <v>168.2553558349609</v>
       </c>
       <c r="C224" t="n">
         <v>170.1999969482422</v>
@@ -6360,7 +6360,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>186.7014617919922</v>
+        <v>186.7014465332031</v>
       </c>
       <c r="C226" t="n">
         <v>188.5800018310547</v>
@@ -6389,7 +6389,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>170.0688323974609</v>
+        <v>170.0688171386719</v>
       </c>
       <c r="C227" t="n">
         <v>171.7799987792969</v>
@@ -6418,7 +6418,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>180.3454132080078</v>
+        <v>180.3454284667969</v>
       </c>
       <c r="C228" t="n">
         <v>182.1600036621094</v>
@@ -6447,7 +6447,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>165.3975372314453</v>
+        <v>165.3975524902344</v>
       </c>
       <c r="C229" t="n">
         <v>166.7899932861328</v>
@@ -6476,7 +6476,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>201.8704681396484</v>
+        <v>201.8704833984375</v>
       </c>
       <c r="C230" t="n">
         <v>203.5700073242188</v>
@@ -6505,7 +6505,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>205.2520141601562</v>
+        <v>205.2520294189453</v>
       </c>
       <c r="C231" t="n">
         <v>206.9799957275391</v>
@@ -6534,7 +6534,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>198.8483123779297</v>
+        <v>198.8482971191406</v>
       </c>
       <c r="C232" t="n">
         <v>200.1499938964844</v>
@@ -6563,7 +6563,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>200.2292633056641</v>
+        <v>200.2292785644531</v>
       </c>
       <c r="C233" t="n">
         <v>201.5399932861328</v>
@@ -6737,7 +6737,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>307.7645874023438</v>
+        <v>307.7645568847656</v>
       </c>
       <c r="C239" t="n">
         <v>308.9500122070312</v>
